--- a/files/Straight_Greyhound_upcoming_rated_prices.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -785,21 +785,12 @@
     <t xml:space="preserve">Kerry Hoggan</t>
   </si>
   <si>
-    <t xml:space="preserve">BENTLEY SVEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Speeding</t>
-  </si>
-  <si>
     <t xml:space="preserve">BLOCKER TIGER</t>
   </si>
   <si>
     <t xml:space="preserve">Stephen Neary</t>
   </si>
   <si>
-    <t xml:space="preserve">TUTA MOMENT</t>
-  </si>
-  <si>
     <t xml:space="preserve">SPEEDY BEN</t>
   </si>
   <si>
@@ -813,6 +804,12 @@
   </si>
   <si>
     <t xml:space="preserve">HOT PINK DOUBLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAKODA SKYLAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAG THE JOKER</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10 13:10:00</t>
@@ -1591,7 +1588,7 @@
         <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S2"/>
       <c r="T2"/>
@@ -1684,7 +1681,7 @@
         <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="S3"/>
       <c r="T3"/>
@@ -1768,7 +1765,7 @@
       </c>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="P4" t="n">
         <v>2.32</v>
@@ -1777,7 +1774,7 @@
         <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="S4"/>
       <c r="T4"/>
@@ -1857,7 +1854,7 @@
         <v>52</v>
       </c>
       <c r="M5" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="N5"/>
       <c r="O5" t="n">
@@ -2061,13 +2058,13 @@
         <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>32.89</v>
+        <v>32.91</v>
       </c>
       <c r="N7" t="n">
         <v>35.15</v>
       </c>
       <c r="O7" t="n">
-        <v>21.18</v>
+        <v>21.2</v>
       </c>
       <c r="P7" t="n">
         <v>13.79</v>
@@ -2584,19 +2581,19 @@
         <v>68</v>
       </c>
       <c r="M12" t="n">
-        <v>27.9</v>
+        <v>27.91</v>
       </c>
       <c r="N12" t="n">
-        <v>30.19</v>
+        <v>30.31</v>
       </c>
       <c r="O12" t="n">
-        <v>46.24</v>
+        <v>46.17</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>11.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="R12" t="n">
         <v>-4</v>
@@ -2698,16 +2695,16 @@
         <v>34.9</v>
       </c>
       <c r="N13" t="n">
-        <v>31.56</v>
+        <v>31.48</v>
       </c>
       <c r="O13" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="P13" t="n">
-        <v>13.85</v>
+        <v>13.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="R13" t="n">
         <v>-4.7</v>
@@ -2804,16 +2801,16 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>51.03</v>
+        <v>51.04</v>
       </c>
       <c r="N14" t="n">
-        <v>41.55</v>
+        <v>41.51</v>
       </c>
       <c r="O14" t="n">
-        <v>25.81</v>
+        <v>25.83</v>
       </c>
       <c r="P14" t="n">
-        <v>19.03</v>
+        <v>19.02</v>
       </c>
       <c r="Q14" t="n">
         <v>9.46</v>
@@ -2916,7 +2913,7 @@
         <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="O15" t="n">
         <v>2.6</v>
@@ -3025,7 +3022,7 @@
         <v>3.22</v>
       </c>
       <c r="N16" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="O16" t="n">
         <v>3.44</v>
@@ -3133,10 +3130,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="n">
-        <v>8.38</v>
+        <v>8.37</v>
       </c>
       <c r="N17" t="n">
-        <v>6.63</v>
+        <v>6.61</v>
       </c>
       <c r="O17" t="n">
         <v>6.84</v>
@@ -3245,10 +3242,10 @@
         <v>13.16</v>
       </c>
       <c r="N18" t="n">
-        <v>9.3</v>
+        <v>9.32</v>
       </c>
       <c r="O18" t="n">
-        <v>18.34</v>
+        <v>18.32</v>
       </c>
       <c r="P18" t="n">
         <v>5.69</v>
@@ -3351,19 +3348,19 @@
         <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>14.05</v>
+        <v>14.06</v>
       </c>
       <c r="N19" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="O19" t="n">
-        <v>15.24</v>
+        <v>15.25</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
         <v>-2.4</v>
@@ -3460,13 +3457,13 @@
         <v>83</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>18.01</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85</v>
+        <v>13.81</v>
       </c>
       <c r="O20" t="n">
-        <v>24.3</v>
+        <v>24.33</v>
       </c>
       <c r="P20" t="n">
         <v>8.04</v>
@@ -3571,16 +3568,16 @@
         <v>85</v>
       </c>
       <c r="M21" t="n">
-        <v>57.43</v>
+        <v>57.42</v>
       </c>
       <c r="N21" t="n">
-        <v>48.2</v>
+        <v>48.38</v>
       </c>
       <c r="O21" t="n">
-        <v>57.14</v>
+        <v>57.07</v>
       </c>
       <c r="P21" t="n">
-        <v>24.31</v>
+        <v>24.32</v>
       </c>
       <c r="Q21" t="n">
         <v>12.59</v>
@@ -3682,7 +3679,7 @@
         <v>80</v>
       </c>
       <c r="M22" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="N22" t="n">
         <v>2.93</v>
@@ -3791,10 +3788,10 @@
         <v>90</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="N23" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="O23" t="n">
         <v>3.79</v>
@@ -3903,16 +3900,16 @@
         <v>9.72</v>
       </c>
       <c r="N24" t="n">
-        <v>7.55</v>
+        <v>7.57</v>
       </c>
       <c r="O24" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
       <c r="P24" t="n">
         <v>4.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="R24" t="n">
         <v>-2</v>
@@ -4009,13 +4006,13 @@
         <v>94</v>
       </c>
       <c r="M25" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="N25" t="n">
-        <v>8.49</v>
+        <v>8.51</v>
       </c>
       <c r="O25" t="n">
-        <v>8.89</v>
+        <v>8.88</v>
       </c>
       <c r="P25" t="n">
         <v>5.11</v>
@@ -4121,10 +4118,10 @@
         <v>13.19</v>
       </c>
       <c r="N26" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="O26" t="n">
-        <v>14.25</v>
+        <v>14.24</v>
       </c>
       <c r="P26" t="n">
         <v>5.78</v>
@@ -4230,10 +4227,10 @@
         <v>19.55</v>
       </c>
       <c r="N27" t="n">
-        <v>22.39</v>
+        <v>22.43</v>
       </c>
       <c r="O27" t="n">
-        <v>24.04</v>
+        <v>24.03</v>
       </c>
       <c r="P27" t="n">
         <v>8.07</v>
@@ -4338,19 +4335,19 @@
         <v>75</v>
       </c>
       <c r="M28" t="n">
-        <v>24.11</v>
+        <v>24.09</v>
       </c>
       <c r="N28" t="n">
-        <v>19.11</v>
+        <v>19.03</v>
       </c>
       <c r="O28" t="n">
-        <v>44.39</v>
+        <v>44.46</v>
       </c>
       <c r="P28" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
         <v>-3.2</v>
@@ -4667,10 +4664,10 @@
         <v>107</v>
       </c>
       <c r="M31" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="N31" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="O31" t="n">
         <v>6.71</v>
@@ -4779,10 +4776,10 @@
         <v>8.57</v>
       </c>
       <c r="N32" t="n">
-        <v>8.62</v>
+        <v>8.61</v>
       </c>
       <c r="O32" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="P32" t="n">
         <v>3.9</v>
@@ -4888,7 +4885,7 @@
         <v>10.02</v>
       </c>
       <c r="N33" t="n">
-        <v>9.57</v>
+        <v>9.59</v>
       </c>
       <c r="O33" t="n">
         <v>12.35</v>
@@ -4997,10 +4994,10 @@
         <v>18.62</v>
       </c>
       <c r="N34" t="n">
-        <v>24.17</v>
+        <v>24.01</v>
       </c>
       <c r="O34" t="n">
-        <v>23.5</v>
+        <v>23.55</v>
       </c>
       <c r="P34" t="n">
         <v>8.13</v>
@@ -5108,13 +5105,13 @@
         <v>25.49</v>
       </c>
       <c r="N35" t="n">
-        <v>24.77</v>
+        <v>24.55</v>
       </c>
       <c r="O35" t="n">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="P35" t="n">
-        <v>11.77</v>
+        <v>11.76</v>
       </c>
       <c r="Q35" t="n">
         <v>6.97</v>
@@ -5219,10 +5216,10 @@
         <v>3.94</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="O36" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="P36" t="n">
         <v>2.09</v>
@@ -5441,10 +5438,10 @@
         <v>5.32</v>
       </c>
       <c r="N38" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
       <c r="O38" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
       <c r="P38" t="n">
         <v>2.63</v>
@@ -5552,7 +5549,7 @@
         <v>8.61</v>
       </c>
       <c r="N39" t="n">
-        <v>7.87</v>
+        <v>7.86</v>
       </c>
       <c r="O39" t="n">
         <v>6.47</v>
@@ -5661,10 +5658,10 @@
         <v>13.17</v>
       </c>
       <c r="N40" t="n">
-        <v>12.38</v>
+        <v>12.35</v>
       </c>
       <c r="O40" t="n">
-        <v>17.65</v>
+        <v>17.67</v>
       </c>
       <c r="P40" t="n">
         <v>6.46</v>
@@ -5673,7 +5670,7 @@
         <v>4.08</v>
       </c>
       <c r="R40" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="S40" t="n">
         <v>101</v>
@@ -5764,10 +5761,10 @@
         <v>16.38</v>
       </c>
       <c r="N41" t="n">
-        <v>14.27</v>
+        <v>14.18</v>
       </c>
       <c r="O41" t="n">
-        <v>12.87</v>
+        <v>12.9</v>
       </c>
       <c r="P41" t="n">
         <v>7.32</v>
@@ -5870,11 +5867,11 @@
         <v>125</v>
       </c>
       <c r="M42" t="n">
-        <v>18.88</v>
+        <v>18.89</v>
       </c>
       <c r="N42"/>
       <c r="O42" t="n">
-        <v>19.69</v>
+        <v>19.72</v>
       </c>
       <c r="P42" t="n">
         <v>9.2</v>
@@ -5963,17 +5960,17 @@
         <v>52</v>
       </c>
       <c r="M43" t="n">
-        <v>24.1</v>
+        <v>24.06</v>
       </c>
       <c r="N43"/>
       <c r="O43" t="n">
-        <v>27.63</v>
+        <v>27.65</v>
       </c>
       <c r="P43" t="n">
-        <v>11.85</v>
+        <v>11.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.36</v>
+        <v>7.35</v>
       </c>
       <c r="R43" t="n">
         <v>-3.1</v>
@@ -6059,10 +6056,10 @@
         <v>3.11</v>
       </c>
       <c r="N44" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="O44" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="P44" t="n">
         <v>1.72</v>
@@ -6170,7 +6167,7 @@
         <v>4.15</v>
       </c>
       <c r="N45" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="O45" t="n">
         <v>3.6</v>
@@ -6281,7 +6278,7 @@
         <v>4.9</v>
       </c>
       <c r="N46" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
         <v>4.02</v>
@@ -6390,10 +6387,10 @@
         <v>7.34</v>
       </c>
       <c r="N47" t="n">
-        <v>6.03</v>
+        <v>6.05</v>
       </c>
       <c r="O47" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
       <c r="P47" t="n">
         <v>3.3</v>
@@ -6496,14 +6493,14 @@
         <v>52</v>
       </c>
       <c r="M48" t="n">
-        <v>20.09</v>
+        <v>20.1</v>
       </c>
       <c r="N48"/>
       <c r="O48" t="n">
-        <v>16.89</v>
+        <v>16.86</v>
       </c>
       <c r="P48" t="n">
-        <v>9.24</v>
+        <v>9.25</v>
       </c>
       <c r="Q48" t="n">
         <v>5.36</v>
@@ -6589,13 +6586,13 @@
         <v>137</v>
       </c>
       <c r="M49" t="n">
-        <v>27.82</v>
+        <v>27.84</v>
       </c>
       <c r="N49" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="O49" t="n">
-        <v>33.53</v>
+        <v>33.48</v>
       </c>
       <c r="P49" t="n">
         <v>12.17</v>
@@ -6698,19 +6695,19 @@
         <v>105</v>
       </c>
       <c r="M50" t="n">
-        <v>89.63</v>
+        <v>89.52</v>
       </c>
       <c r="N50" t="n">
         <v>69.89</v>
       </c>
       <c r="O50" t="n">
-        <v>98.91</v>
+        <v>98.79</v>
       </c>
       <c r="P50" t="n">
-        <v>39.42</v>
+        <v>39.45</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="R50" t="n">
         <v>-5.1</v>
@@ -6812,7 +6809,7 @@
         <v>3.52</v>
       </c>
       <c r="N51" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
         <v>3.26</v>
@@ -6921,7 +6918,7 @@
         <v>4.21</v>
       </c>
       <c r="N52" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="O52" t="n">
         <v>4.77</v>
@@ -7027,13 +7024,13 @@
         <v>59</v>
       </c>
       <c r="M53" t="n">
-        <v>5.87</v>
+        <v>5.88</v>
       </c>
       <c r="N53" t="n">
-        <v>6.76</v>
+        <v>6.75</v>
       </c>
       <c r="O53" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="P53" t="n">
         <v>2.89</v>
@@ -7139,7 +7136,7 @@
         <v>9.4</v>
       </c>
       <c r="N54" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="O54" t="n">
         <v>18.21</v>
@@ -7245,13 +7242,13 @@
         <v>103</v>
       </c>
       <c r="M55" t="n">
-        <v>9.65</v>
+        <v>9.64</v>
       </c>
       <c r="N55" t="n">
-        <v>7.82</v>
+        <v>7.76</v>
       </c>
       <c r="O55" t="n">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="P55" t="n">
         <v>4.48</v>
@@ -7260,7 +7257,7 @@
         <v>2.76</v>
       </c>
       <c r="R55" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="S55" t="n">
         <v>104.7</v>
@@ -7465,16 +7462,16 @@
         <v>149</v>
       </c>
       <c r="M57" t="n">
-        <v>61.22</v>
+        <v>61.26</v>
       </c>
       <c r="N57" t="n">
-        <v>49.73</v>
+        <v>49.78</v>
       </c>
       <c r="O57" t="n">
-        <v>101.09</v>
+        <v>101.04</v>
       </c>
       <c r="P57" t="n">
-        <v>26.58</v>
+        <v>26.56</v>
       </c>
       <c r="Q57" t="n">
         <v>14.86</v>
@@ -7574,13 +7571,13 @@
         <v>112</v>
       </c>
       <c r="M58" t="n">
-        <v>63.56</v>
+        <v>63.58</v>
       </c>
       <c r="N58" t="n">
-        <v>59.78</v>
+        <v>59.92</v>
       </c>
       <c r="O58" t="n">
-        <v>84.58</v>
+        <v>84.48</v>
       </c>
       <c r="P58" t="n">
         <v>27.82</v>
@@ -7688,10 +7685,10 @@
         <v>2.81</v>
       </c>
       <c r="N59" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="O59" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P59" t="n">
         <v>1.62</v>
@@ -7799,7 +7796,7 @@
         <v>4.77</v>
       </c>
       <c r="N60" t="n">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
       <c r="O60" t="n">
         <v>3.39</v>
@@ -8018,19 +8015,19 @@
         <v>159</v>
       </c>
       <c r="M62" t="n">
-        <v>10.64</v>
+        <v>10.62</v>
       </c>
       <c r="N62" t="n">
-        <v>8.46</v>
+        <v>8.41</v>
       </c>
       <c r="O62" t="n">
-        <v>9.78</v>
+        <v>9.8</v>
       </c>
       <c r="P62" t="n">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="R62" t="n">
         <v>-2</v>
@@ -8130,13 +8127,13 @@
         <v>11.95</v>
       </c>
       <c r="N63" t="n">
-        <v>9.71</v>
+        <v>9.7</v>
       </c>
       <c r="O63" t="n">
-        <v>17.55</v>
+        <v>17.56</v>
       </c>
       <c r="P63" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="Q63" t="n">
         <v>3.03</v>
@@ -8239,16 +8236,16 @@
         <v>13.18</v>
       </c>
       <c r="N64" t="n">
-        <v>10.01</v>
+        <v>10.03</v>
       </c>
       <c r="O64" t="n">
-        <v>20.08</v>
+        <v>20.07</v>
       </c>
       <c r="P64" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="R64" t="n">
         <v>-2.4</v>
@@ -8348,7 +8345,7 @@
         <v>2.61</v>
       </c>
       <c r="N65" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="O65" t="n">
         <v>1.78</v>
@@ -8460,7 +8457,7 @@
         <v>3.29</v>
       </c>
       <c r="O66" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="P66" t="n">
         <v>1.67</v>
@@ -8565,19 +8562,19 @@
         <v>166</v>
       </c>
       <c r="M67" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="N67" t="n">
         <v>10.7</v>
       </c>
       <c r="O67" t="n">
-        <v>30.84</v>
+        <v>30.83</v>
       </c>
       <c r="P67" t="n">
         <v>5.06</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="R67" t="n">
         <v>-2.3</v>
@@ -8679,7 +8676,7 @@
         <v>15.79</v>
       </c>
       <c r="N68" t="n">
-        <v>12.79</v>
+        <v>12.77</v>
       </c>
       <c r="O68" t="n">
         <v>35.38</v>
@@ -8787,16 +8784,16 @@
         <v>149</v>
       </c>
       <c r="M69" t="n">
-        <v>17.11</v>
+        <v>17.13</v>
       </c>
       <c r="N69" t="n">
-        <v>14.33</v>
+        <v>14.36</v>
       </c>
       <c r="O69" t="n">
-        <v>25.56</v>
+        <v>25.51</v>
       </c>
       <c r="P69" t="n">
-        <v>7.08</v>
+        <v>7.09</v>
       </c>
       <c r="Q69" t="n">
         <v>3.79</v>
@@ -8898,13 +8895,13 @@
         <v>83</v>
       </c>
       <c r="M70" t="n">
-        <v>17.73</v>
+        <v>17.74</v>
       </c>
       <c r="N70" t="n">
-        <v>18.72</v>
+        <v>18.76</v>
       </c>
       <c r="O70" t="n">
-        <v>22.92</v>
+        <v>22.91</v>
       </c>
       <c r="P70" t="n">
         <v>7.48</v>
@@ -9009,19 +9006,19 @@
         <v>109</v>
       </c>
       <c r="M71" t="n">
-        <v>26.89</v>
+        <v>26.94</v>
       </c>
       <c r="N71" t="n">
-        <v>19.85</v>
+        <v>19.95</v>
       </c>
       <c r="O71" t="n">
-        <v>47.08</v>
+        <v>46.98</v>
       </c>
       <c r="P71" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="R71" t="n">
         <v>-3.6</v>
@@ -9118,19 +9115,19 @@
         <v>172</v>
       </c>
       <c r="M72" t="n">
-        <v>145.08</v>
+        <v>145.03</v>
       </c>
       <c r="N72" t="n">
         <v>88.42</v>
       </c>
       <c r="O72" t="n">
-        <v>239.29</v>
+        <v>239.01</v>
       </c>
       <c r="P72" t="n">
-        <v>61.98</v>
+        <v>61.99</v>
       </c>
       <c r="Q72" t="n">
-        <v>32.56</v>
+        <v>32.58</v>
       </c>
       <c r="R72" t="n">
         <v>-6.3</v>
@@ -9338,13 +9335,13 @@
         <v>176</v>
       </c>
       <c r="M74" t="n">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="N74" t="n">
-        <v>12.54</v>
+        <v>12.44</v>
       </c>
       <c r="O74" t="n">
-        <v>10.36</v>
+        <v>10.38</v>
       </c>
       <c r="P74" t="n">
         <v>3.81</v>
@@ -9449,7 +9446,7 @@
         <v>109</v>
       </c>
       <c r="M75" t="n">
-        <v>15.52</v>
+        <v>15.53</v>
       </c>
       <c r="N75" t="n">
         <v>13.25</v>
@@ -9558,14 +9555,14 @@
         <v>119</v>
       </c>
       <c r="M76" t="n">
-        <v>18.16</v>
+        <v>18.14</v>
       </c>
       <c r="N76"/>
       <c r="O76" t="n">
-        <v>14.92</v>
+        <v>14.93</v>
       </c>
       <c r="P76" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="Q76" t="n">
         <v>2.88</v>
@@ -9651,13 +9648,13 @@
         <v>180</v>
       </c>
       <c r="M77" t="n">
-        <v>18.97</v>
+        <v>18.99</v>
       </c>
       <c r="N77" t="n">
-        <v>15.08</v>
+        <v>15.09</v>
       </c>
       <c r="O77" t="n">
-        <v>24.19</v>
+        <v>24.18</v>
       </c>
       <c r="P77" t="n">
         <v>5.07</v>
@@ -9765,16 +9762,16 @@
         <v>29.73</v>
       </c>
       <c r="N78" t="n">
-        <v>25.26</v>
+        <v>25.25</v>
       </c>
       <c r="O78" t="n">
-        <v>38.28</v>
+        <v>38.3</v>
       </c>
       <c r="P78" t="n">
         <v>7.91</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="R78" t="n">
         <v>-4.9</v>
@@ -9871,16 +9868,16 @@
         <v>107</v>
       </c>
       <c r="M79" t="n">
-        <v>60.96</v>
+        <v>60.94</v>
       </c>
       <c r="N79" t="n">
-        <v>58.11</v>
+        <v>57.91</v>
       </c>
       <c r="O79" t="n">
-        <v>130.19</v>
+        <v>130.52</v>
       </c>
       <c r="P79" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="Q79" t="n">
         <v>9.24</v>
@@ -9982,19 +9979,19 @@
         <v>80</v>
       </c>
       <c r="M80" t="n">
-        <v>138.77</v>
+        <v>138.83</v>
       </c>
       <c r="N80" t="n">
         <v>131.76</v>
       </c>
       <c r="O80" t="n">
-        <v>187.96</v>
+        <v>188.23</v>
       </c>
       <c r="P80" t="n">
-        <v>42.42</v>
+        <v>42.46</v>
       </c>
       <c r="Q80" t="n">
-        <v>20.74</v>
+        <v>20.75</v>
       </c>
       <c r="R80" t="n">
         <v>-7.7</v>
@@ -10205,7 +10202,7 @@
         <v>4.61</v>
       </c>
       <c r="N82" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="O82" t="n">
         <v>3.14</v>
@@ -10314,7 +10311,7 @@
         <v>6.27</v>
       </c>
       <c r="N83" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="O83" t="n">
         <v>5.18</v>
@@ -10326,7 +10323,7 @@
         <v>1.97</v>
       </c>
       <c r="R83" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="S83" t="n">
         <v>105.7</v>
@@ -10420,13 +10417,13 @@
         <v>96</v>
       </c>
       <c r="M84" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="N84" t="n">
-        <v>6.52</v>
+        <v>6.49</v>
       </c>
       <c r="O84" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="P84" t="n">
         <v>3.45</v>
@@ -10532,7 +10529,7 @@
         <v>11.04</v>
       </c>
       <c r="N85" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
       <c r="O85" t="n">
         <v>16.89</v>
@@ -10641,10 +10638,10 @@
         <v>16.63</v>
       </c>
       <c r="N86" t="n">
-        <v>22.79</v>
+        <v>22.84</v>
       </c>
       <c r="O86" t="n">
-        <v>24.37</v>
+        <v>24.35</v>
       </c>
       <c r="P86" t="n">
         <v>7.42</v>
@@ -10749,16 +10746,16 @@
         <v>107</v>
       </c>
       <c r="M87" t="n">
-        <v>34.16</v>
+        <v>34.2</v>
       </c>
       <c r="N87" t="n">
-        <v>42.61</v>
+        <v>42.79</v>
       </c>
       <c r="O87" t="n">
-        <v>84.58</v>
+        <v>84.57</v>
       </c>
       <c r="P87" t="n">
-        <v>15.07</v>
+        <v>15.08</v>
       </c>
       <c r="Q87" t="n">
         <v>8.46</v>
@@ -14262,19 +14259,19 @@
         <v>256</v>
       </c>
       <c r="M120" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="N120" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="O120" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="P120" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="R120" t="n">
         <v>1.3</v>
@@ -14364,7 +14361,7 @@
       </c>
       <c r="I121"/>
       <c r="J121" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K121" t="s">
         <v>257</v>
@@ -14373,67 +14370,67 @@
         <v>258</v>
       </c>
       <c r="M121" t="n">
-        <v>5.38</v>
+        <v>4.23</v>
       </c>
       <c r="N121" t="n">
-        <v>4.65</v>
+        <v>4.06</v>
       </c>
       <c r="O121" t="n">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="P121" t="n">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="R121" t="n">
         <v>-1.3</v>
       </c>
       <c r="S121" t="n">
-        <v>103.6</v>
+        <v>101.3</v>
       </c>
       <c r="T121" t="n">
-        <v>103.6</v>
+        <v>104.1</v>
       </c>
       <c r="U121" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="V121" t="n">
-        <v>103.1</v>
+        <v>105</v>
       </c>
       <c r="W121" t="n">
-        <v>95.1</v>
+        <v>100.7</v>
       </c>
       <c r="X121" t="n">
-        <v>103.6</v>
+        <v>105</v>
       </c>
       <c r="Y121" t="n">
-        <v>103.7</v>
+        <v>105</v>
       </c>
       <c r="Z121" t="n">
-        <v>103.3</v>
+        <v>104.1</v>
       </c>
       <c r="AA121" t="n">
-        <v>103.3</v>
+        <v>108.3</v>
       </c>
       <c r="AB121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AC121" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AD121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AF121" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="AG121" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="AH121" t="n">
         <v>0</v>
@@ -14475,7 +14472,7 @@
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K122" t="s">
         <v>259</v>
@@ -14484,73 +14481,67 @@
         <v>260</v>
       </c>
       <c r="M122" t="n">
-        <v>5.76</v>
+        <v>16.51</v>
       </c>
       <c r="N122" t="n">
-        <v>6.01</v>
+        <v>12.82</v>
       </c>
       <c r="O122" t="n">
-        <v>5.06</v>
+        <v>24.01</v>
       </c>
       <c r="P122" t="n">
-        <v>2.6</v>
+        <v>6.32</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.65</v>
+        <v>3.04</v>
       </c>
       <c r="R122" t="n">
-        <v>-1.3</v>
+        <v>-3.4</v>
       </c>
       <c r="S122" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="T122" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="U122" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="V122" t="n">
         <v>101.3</v>
       </c>
-      <c r="T122" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="U122" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="V122" t="n">
-        <v>105</v>
-      </c>
       <c r="W122" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="X122" t="n">
         <v>100.7</v>
       </c>
-      <c r="X122" t="n">
-        <v>105</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>105</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>108.3</v>
-      </c>
+      <c r="Y122"/>
+      <c r="Z122"/>
+      <c r="AA122"/>
       <c r="AB122" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC122" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE122" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AF122" t="n">
+        <v>59</v>
+      </c>
+      <c r="AG122" t="n">
         <v>64</v>
       </c>
-      <c r="AG122" t="n">
-        <v>79</v>
-      </c>
       <c r="AH122" t="n">
         <v>0</v>
       </c>
       <c r="AI122" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AJ122" t="s">
         <v>46</v>
@@ -14586,76 +14577,76 @@
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K123" t="s">
         <v>261</v>
       </c>
       <c r="L123" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M123" t="n">
-        <v>9.43</v>
+        <v>24.6</v>
       </c>
       <c r="N123" t="n">
-        <v>7.3</v>
+        <v>18.62</v>
       </c>
       <c r="O123" t="n">
-        <v>31.98</v>
+        <v>69.12</v>
       </c>
       <c r="P123" t="n">
-        <v>4.14</v>
+        <v>8.54</v>
       </c>
       <c r="Q123" t="n">
-        <v>2.45</v>
+        <v>3.82</v>
       </c>
       <c r="R123" t="n">
-        <v>-2.3</v>
+        <v>-3.8</v>
       </c>
       <c r="S123" t="n">
-        <v>104.6</v>
+        <v>97.2</v>
       </c>
       <c r="T123" t="n">
-        <v>102.8</v>
+        <v>97.2</v>
       </c>
       <c r="U123" t="n">
-        <v>99.2</v>
+        <v>97.2</v>
       </c>
       <c r="V123" t="n">
         <v>103.1</v>
       </c>
       <c r="W123" t="n">
+        <v>98.1</v>
+      </c>
+      <c r="X123" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="Y123" t="n">
         <v>98.5</v>
       </c>
-      <c r="X123" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>99.2</v>
-      </c>
       <c r="Z123" t="n">
-        <v>99.2</v>
+        <v>100.7</v>
       </c>
       <c r="AA123" t="n">
-        <v>99.2</v>
+        <v>100.8</v>
       </c>
       <c r="AB123" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AC123" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AD123" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AE123" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AF123" t="n">
         <v>17</v>
       </c>
       <c r="AG123" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AH123" t="n">
         <v>0</v>
@@ -14697,76 +14688,76 @@
       </c>
       <c r="I124"/>
       <c r="J124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K124" t="s">
         <v>262</v>
       </c>
       <c r="L124" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="M124" t="n">
-        <v>22.83</v>
+        <v>26.56</v>
       </c>
       <c r="N124" t="n">
-        <v>19.02</v>
+        <v>15.32</v>
       </c>
       <c r="O124" t="n">
-        <v>33.08</v>
+        <v>79.36</v>
       </c>
       <c r="P124" t="n">
-        <v>9.93</v>
+        <v>10.65</v>
       </c>
       <c r="Q124" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="R124" t="n">
-        <v>-3.5</v>
+        <v>-4.7</v>
       </c>
       <c r="S124" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="T124" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="U124" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="V124" t="n">
         <v>102.2</v>
       </c>
-      <c r="T124" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="U124" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="V124" t="n">
-        <v>101.3</v>
-      </c>
       <c r="W124" t="n">
-        <v>100.9</v>
+        <v>98.5</v>
       </c>
       <c r="X124" t="n">
-        <v>100.7</v>
+        <v>96.8</v>
       </c>
       <c r="Y124"/>
       <c r="Z124"/>
       <c r="AA124"/>
       <c r="AB124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE124" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AF124" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="AG124" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="AH124" t="n">
         <v>0</v>
       </c>
       <c r="AI124" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="AJ124" t="s">
         <v>46</v>
@@ -14802,31 +14793,31 @@
       </c>
       <c r="I125"/>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K125" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L125" t="s">
-        <v>249</v>
+        <v>210</v>
       </c>
       <c r="M125" t="n">
-        <v>35.71</v>
+        <v>30.61</v>
       </c>
       <c r="N125" t="n">
-        <v>30.08</v>
+        <v>24.17</v>
       </c>
       <c r="O125" t="n">
-        <v>96.05</v>
+        <v>73.94</v>
       </c>
       <c r="P125" t="n">
-        <v>14.48</v>
+        <v>10.46</v>
       </c>
       <c r="Q125" t="n">
-        <v>7.58</v>
+        <v>4.63</v>
       </c>
       <c r="R125" t="n">
-        <v>-3.9</v>
+        <v>-4.1</v>
       </c>
       <c r="S125" t="n">
         <v>97.2</v>
@@ -14838,40 +14829,40 @@
         <v>97.2</v>
       </c>
       <c r="V125" t="n">
-        <v>103.1</v>
+        <v>102.1</v>
       </c>
       <c r="W125" t="n">
-        <v>98.1</v>
+        <v>98.9</v>
       </c>
       <c r="X125" t="n">
-        <v>97.3</v>
+        <v>96.8</v>
       </c>
       <c r="Y125" t="n">
-        <v>98.5</v>
+        <v>97.7</v>
       </c>
       <c r="Z125" t="n">
-        <v>100.7</v>
+        <v>97.4</v>
       </c>
       <c r="AA125" t="n">
-        <v>100.8</v>
+        <v>98.7</v>
       </c>
       <c r="AB125" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AC125" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AD125" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AE125" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="AF125" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AG125" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="AH125" t="n">
         <v>0</v>
@@ -14913,70 +14904,76 @@
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K126" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L126" t="s">
-        <v>249</v>
+        <v>109</v>
       </c>
       <c r="M126" t="n">
-        <v>37.41</v>
+        <v>44.92</v>
       </c>
       <c r="N126" t="n">
-        <v>22.91</v>
+        <v>36.81</v>
       </c>
       <c r="O126" t="n">
-        <v>109.37</v>
+        <v>147.97</v>
       </c>
       <c r="P126" t="n">
-        <v>16.75</v>
+        <v>16.13</v>
       </c>
       <c r="Q126" t="n">
-        <v>9.54</v>
+        <v>7.16</v>
       </c>
       <c r="R126" t="n">
         <v>-4.7</v>
       </c>
       <c r="S126" t="n">
-        <v>94.7</v>
+        <v>92.4</v>
       </c>
       <c r="T126" t="n">
-        <v>95.8</v>
+        <v>92.8</v>
       </c>
       <c r="U126" t="n">
-        <v>95.8</v>
+        <v>94.5</v>
       </c>
       <c r="V126" t="n">
-        <v>102.2</v>
+        <v>103.9</v>
       </c>
       <c r="W126" t="n">
-        <v>98.5</v>
+        <v>96.1</v>
       </c>
       <c r="X126" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="Y126"/>
-      <c r="Z126"/>
-      <c r="AA126"/>
+        <v>95</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>92.8</v>
+      </c>
       <c r="AB126" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD126" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AE126" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AF126" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AG126" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="AH126" t="n">
         <v>0</v>
@@ -15018,76 +15015,76 @@
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L127" t="s">
         <v>210</v>
       </c>
       <c r="M127" t="n">
-        <v>44.46</v>
+        <v>49.35</v>
       </c>
       <c r="N127" t="n">
-        <v>39.73</v>
+        <v>35.1</v>
       </c>
       <c r="O127" t="n">
-        <v>102.97</v>
+        <v>118.2</v>
       </c>
       <c r="P127" t="n">
-        <v>17.86</v>
+        <v>16.94</v>
       </c>
       <c r="Q127" t="n">
-        <v>9.25</v>
+        <v>7.4</v>
       </c>
       <c r="R127" t="n">
-        <v>-4.1</v>
+        <v>-4.8</v>
       </c>
       <c r="S127" t="n">
-        <v>97.2</v>
+        <v>93.1</v>
       </c>
       <c r="T127" t="n">
-        <v>97.2</v>
+        <v>95.5</v>
       </c>
       <c r="U127" t="n">
-        <v>97.2</v>
+        <v>95.5</v>
       </c>
       <c r="V127" t="n">
-        <v>102.1</v>
+        <v>103</v>
       </c>
       <c r="W127" t="n">
-        <v>98.9</v>
+        <v>99</v>
       </c>
       <c r="X127" t="n">
-        <v>96.8</v>
+        <v>96</v>
       </c>
       <c r="Y127" t="n">
-        <v>97.7</v>
+        <v>94.9</v>
       </c>
       <c r="Z127" t="n">
-        <v>97.4</v>
+        <v>93.9</v>
       </c>
       <c r="AA127" t="n">
-        <v>98.7</v>
+        <v>96.5</v>
       </c>
       <c r="AB127" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AC127" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD127" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE127" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AF127" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AG127" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AH127" t="n">
         <v>0</v>
@@ -15113,7 +15110,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E128" t="n">
         <v>350</v>
@@ -15132,10 +15129,10 @@
         <v>4</v>
       </c>
       <c r="K128" t="s">
+        <v>267</v>
+      </c>
+      <c r="L128" t="s">
         <v>268</v>
-      </c>
-      <c r="L128" t="s">
-        <v>269</v>
       </c>
       <c r="M128" t="n">
         <v>2.78</v>
@@ -15224,7 +15221,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E129" t="n">
         <v>350</v>
@@ -15243,7 +15240,7 @@
         <v>1</v>
       </c>
       <c r="K129" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L129" t="s">
         <v>213</v>
@@ -15335,7 +15332,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E130" t="n">
         <v>350</v>
@@ -15354,7 +15351,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L130" t="s">
         <v>249</v>
@@ -15446,7 +15443,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E131" t="n">
         <v>350</v>
@@ -15465,10 +15462,10 @@
         <v>7</v>
       </c>
       <c r="K131" t="s">
+        <v>271</v>
+      </c>
+      <c r="L131" t="s">
         <v>272</v>
-      </c>
-      <c r="L131" t="s">
-        <v>273</v>
       </c>
       <c r="M131" t="n">
         <v>8.12</v>
@@ -15551,7 +15548,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E132" t="n">
         <v>350</v>
@@ -15570,10 +15567,10 @@
         <v>8</v>
       </c>
       <c r="K132" t="s">
+        <v>273</v>
+      </c>
+      <c r="L132" t="s">
         <v>274</v>
-      </c>
-      <c r="L132" t="s">
-        <v>275</v>
       </c>
       <c r="M132" t="n">
         <v>19.9</v>
@@ -15656,7 +15653,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E133" t="n">
         <v>350</v>
@@ -15675,10 +15672,10 @@
         <v>5</v>
       </c>
       <c r="K133" t="s">
+        <v>275</v>
+      </c>
+      <c r="L133" t="s">
         <v>276</v>
-      </c>
-      <c r="L133" t="s">
-        <v>277</v>
       </c>
       <c r="M133" t="n">
         <v>20.24</v>
@@ -15749,7 +15746,7 @@
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E134" t="n">
         <v>350</v>
@@ -15768,7 +15765,7 @@
         <v>3</v>
       </c>
       <c r="K134" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L134" t="s">
         <v>219</v>
@@ -15860,7 +15857,7 @@
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E135" t="n">
         <v>350</v>
@@ -15879,10 +15876,10 @@
         <v>6</v>
       </c>
       <c r="K135" t="s">
+        <v>278</v>
+      </c>
+      <c r="L135" t="s">
         <v>279</v>
-      </c>
-      <c r="L135" t="s">
-        <v>280</v>
       </c>
       <c r="M135" t="n">
         <v>149.83</v>
@@ -15971,13 +15968,13 @@
         <v>7</v>
       </c>
       <c r="D136" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E136" t="n">
         <v>350</v>
       </c>
       <c r="F136" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
@@ -15990,10 +15987,10 @@
         <v>3</v>
       </c>
       <c r="K136" t="s">
+        <v>282</v>
+      </c>
+      <c r="L136" t="s">
         <v>283</v>
-      </c>
-      <c r="L136" t="s">
-        <v>284</v>
       </c>
       <c r="M136" t="n">
         <v>3.04</v>
@@ -16082,13 +16079,13 @@
         <v>7</v>
       </c>
       <c r="D137" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E137" t="n">
         <v>350</v>
       </c>
       <c r="F137" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
@@ -16101,7 +16098,7 @@
         <v>8</v>
       </c>
       <c r="K137" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L137" t="s">
         <v>219</v>
@@ -16193,13 +16190,13 @@
         <v>7</v>
       </c>
       <c r="D138" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E138" t="n">
         <v>350</v>
       </c>
       <c r="F138" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G138" t="s">
         <v>41</v>
@@ -16212,10 +16209,10 @@
         <v>1</v>
       </c>
       <c r="K138" t="s">
+        <v>285</v>
+      </c>
+      <c r="L138" t="s">
         <v>286</v>
-      </c>
-      <c r="L138" t="s">
-        <v>287</v>
       </c>
       <c r="M138" t="n">
         <v>8.22</v>
@@ -16304,13 +16301,13 @@
         <v>7</v>
       </c>
       <c r="D139" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E139" t="n">
         <v>350</v>
       </c>
       <c r="F139" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G139" t="s">
         <v>41</v>
@@ -16323,7 +16320,7 @@
         <v>4</v>
       </c>
       <c r="K139" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L139" t="s">
         <v>109</v>
@@ -16409,13 +16406,13 @@
         <v>7</v>
       </c>
       <c r="D140" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E140" t="n">
         <v>350</v>
       </c>
       <c r="F140" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G140" t="s">
         <v>41</v>
@@ -16428,10 +16425,10 @@
         <v>6</v>
       </c>
       <c r="K140" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L140" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M140" t="n">
         <v>15.79</v>
@@ -16520,13 +16517,13 @@
         <v>7</v>
       </c>
       <c r="D141" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E141" t="n">
         <v>350</v>
       </c>
       <c r="F141" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G141" t="s">
         <v>41</v>
@@ -16539,10 +16536,10 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L141" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M141" t="n">
         <v>21.11</v>
@@ -16631,13 +16628,13 @@
         <v>7</v>
       </c>
       <c r="D142" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E142" t="n">
         <v>350</v>
       </c>
       <c r="F142" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G142" t="s">
         <v>41</v>
@@ -16650,10 +16647,10 @@
         <v>5</v>
       </c>
       <c r="K142" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L142" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M142" t="n">
         <v>34.94</v>
@@ -16742,13 +16739,13 @@
         <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E143" t="n">
         <v>350</v>
       </c>
       <c r="F143" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G143" t="s">
         <v>41</v>
@@ -16761,7 +16758,7 @@
         <v>7</v>
       </c>
       <c r="K143" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L143" t="s">
         <v>249</v>
@@ -16853,13 +16850,13 @@
         <v>8</v>
       </c>
       <c r="D144" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E144" t="n">
         <v>350</v>
       </c>
       <c r="F144" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G144" t="s">
         <v>41</v>
@@ -16872,10 +16869,10 @@
         <v>1</v>
       </c>
       <c r="K144" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L144" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M144" t="n">
         <v>2.78</v>
@@ -16964,13 +16961,13 @@
         <v>8</v>
       </c>
       <c r="D145" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E145" t="n">
         <v>350</v>
       </c>
       <c r="F145" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G145" t="s">
         <v>41</v>
@@ -16983,7 +16980,7 @@
         <v>3</v>
       </c>
       <c r="K145" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L145" t="s">
         <v>213</v>
@@ -17075,13 +17072,13 @@
         <v>8</v>
       </c>
       <c r="D146" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E146" t="n">
         <v>350</v>
       </c>
       <c r="F146" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G146" t="s">
         <v>41</v>
@@ -17094,7 +17091,7 @@
         <v>8</v>
       </c>
       <c r="K146" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L146" t="s">
         <v>253</v>
@@ -17186,13 +17183,13 @@
         <v>8</v>
       </c>
       <c r="D147" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E147" t="n">
         <v>350</v>
       </c>
       <c r="F147" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
@@ -17205,10 +17202,10 @@
         <v>7</v>
       </c>
       <c r="K147" t="s">
+        <v>297</v>
+      </c>
+      <c r="L147" t="s">
         <v>298</v>
-      </c>
-      <c r="L147" t="s">
-        <v>299</v>
       </c>
       <c r="M147" t="n">
         <v>8.73</v>
@@ -17297,13 +17294,13 @@
         <v>8</v>
       </c>
       <c r="D148" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E148" t="n">
         <v>350</v>
       </c>
       <c r="F148" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
@@ -17316,10 +17313,10 @@
         <v>2</v>
       </c>
       <c r="K148" t="s">
+        <v>299</v>
+      </c>
+      <c r="L148" t="s">
         <v>300</v>
-      </c>
-      <c r="L148" t="s">
-        <v>301</v>
       </c>
       <c r="M148" t="n">
         <v>11.47</v>
@@ -17408,13 +17405,13 @@
         <v>8</v>
       </c>
       <c r="D149" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E149" t="n">
         <v>350</v>
       </c>
       <c r="F149" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G149" t="s">
         <v>41</v>
@@ -17427,10 +17424,10 @@
         <v>4</v>
       </c>
       <c r="K149" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L149" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M149" t="n">
         <v>13.46</v>
@@ -17519,13 +17516,13 @@
         <v>8</v>
       </c>
       <c r="D150" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E150" t="n">
         <v>350</v>
       </c>
       <c r="F150" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G150" t="s">
         <v>41</v>
@@ -17538,10 +17535,10 @@
         <v>6</v>
       </c>
       <c r="K150" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L150" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M150" t="n">
         <v>15.36</v>
@@ -17630,13 +17627,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E151" t="n">
         <v>350</v>
       </c>
       <c r="F151" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G151" t="s">
         <v>41</v>
@@ -17649,10 +17646,10 @@
         <v>1</v>
       </c>
       <c r="K151" t="s">
+        <v>305</v>
+      </c>
+      <c r="L151" t="s">
         <v>306</v>
-      </c>
-      <c r="L151" t="s">
-        <v>307</v>
       </c>
       <c r="M151" t="n">
         <v>1.32</v>
@@ -17741,13 +17738,13 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E152" t="n">
         <v>350</v>
       </c>
       <c r="F152" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G152" t="s">
         <v>41</v>
@@ -17760,7 +17757,7 @@
         <v>6</v>
       </c>
       <c r="K152" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L152" t="s">
         <v>105</v>
@@ -17852,13 +17849,13 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E153" t="n">
         <v>350</v>
       </c>
       <c r="F153" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G153" t="s">
         <v>41</v>
@@ -17871,7 +17868,7 @@
         <v>5</v>
       </c>
       <c r="K153" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L153" t="s">
         <v>243</v>
@@ -17963,13 +17960,13 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E154" t="n">
         <v>350</v>
       </c>
       <c r="F154" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G154" t="s">
         <v>41</v>
@@ -17982,10 +17979,10 @@
         <v>8</v>
       </c>
       <c r="K154" t="s">
+        <v>309</v>
+      </c>
+      <c r="L154" t="s">
         <v>310</v>
-      </c>
-      <c r="L154" t="s">
-        <v>311</v>
       </c>
       <c r="M154" t="n">
         <v>37.55</v>
@@ -18074,13 +18071,13 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E155" t="n">
         <v>350</v>
       </c>
       <c r="F155" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G155" t="s">
         <v>41</v>
@@ -18093,7 +18090,7 @@
         <v>7</v>
       </c>
       <c r="K155" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L155" t="s">
         <v>213</v>
@@ -18185,13 +18182,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E156" t="n">
         <v>350</v>
       </c>
       <c r="F156" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G156" t="s">
         <v>41</v>
@@ -18204,10 +18201,10 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
+        <v>312</v>
+      </c>
+      <c r="L156" t="s">
         <v>313</v>
-      </c>
-      <c r="L156" t="s">
-        <v>314</v>
       </c>
       <c r="M156" t="n">
         <v>43.48</v>
@@ -18296,13 +18293,13 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E157" t="n">
         <v>350</v>
       </c>
       <c r="F157" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G157" t="s">
         <v>41</v>
@@ -18315,7 +18312,7 @@
         <v>4</v>
       </c>
       <c r="K157" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L157" t="s">
         <v>232</v>
@@ -18407,13 +18404,13 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E158" t="n">
         <v>350</v>
       </c>
       <c r="F158" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G158" t="s">
         <v>41</v>
@@ -18426,10 +18423,10 @@
         <v>2</v>
       </c>
       <c r="K158" t="s">
+        <v>315</v>
+      </c>
+      <c r="L158" t="s">
         <v>316</v>
-      </c>
-      <c r="L158" t="s">
-        <v>317</v>
       </c>
       <c r="M158" t="n">
         <v>159.47</v>
@@ -18518,13 +18515,13 @@
         <v>10</v>
       </c>
       <c r="D159" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E159" t="n">
         <v>350</v>
       </c>
       <c r="F159" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G159" t="s">
         <v>41</v>
@@ -18537,10 +18534,10 @@
         <v>5</v>
       </c>
       <c r="K159" t="s">
+        <v>318</v>
+      </c>
+      <c r="L159" t="s">
         <v>319</v>
-      </c>
-      <c r="L159" t="s">
-        <v>320</v>
       </c>
       <c r="M159" t="n">
         <v>3.58</v>
@@ -18629,13 +18626,13 @@
         <v>10</v>
       </c>
       <c r="D160" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E160" t="n">
         <v>350</v>
       </c>
       <c r="F160" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G160" t="s">
         <v>41</v>
@@ -18648,10 +18645,10 @@
         <v>4</v>
       </c>
       <c r="K160" t="s">
+        <v>320</v>
+      </c>
+      <c r="L160" t="s">
         <v>321</v>
-      </c>
-      <c r="L160" t="s">
-        <v>322</v>
       </c>
       <c r="M160" t="n">
         <v>5.02</v>
@@ -18740,13 +18737,13 @@
         <v>10</v>
       </c>
       <c r="D161" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E161" t="n">
         <v>350</v>
       </c>
       <c r="F161" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G161" t="s">
         <v>41</v>
@@ -18759,7 +18756,7 @@
         <v>1</v>
       </c>
       <c r="K161" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L161" t="s">
         <v>105</v>
@@ -18851,13 +18848,13 @@
         <v>10</v>
       </c>
       <c r="D162" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E162" t="n">
         <v>350</v>
       </c>
       <c r="F162" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G162" t="s">
         <v>41</v>
@@ -18870,7 +18867,7 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L162" t="s">
         <v>256</v>
@@ -18962,13 +18959,13 @@
         <v>10</v>
       </c>
       <c r="D163" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E163" t="n">
         <v>350</v>
       </c>
       <c r="F163" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G163" t="s">
         <v>41</v>
@@ -18981,10 +18978,10 @@
         <v>7</v>
       </c>
       <c r="K163" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L163" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M163" t="n">
         <v>9.29</v>
@@ -19073,13 +19070,13 @@
         <v>10</v>
       </c>
       <c r="D164" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E164" t="n">
         <v>350</v>
       </c>
       <c r="F164" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G164" t="s">
         <v>41</v>
@@ -19092,10 +19089,10 @@
         <v>2</v>
       </c>
       <c r="K164" t="s">
+        <v>325</v>
+      </c>
+      <c r="L164" t="s">
         <v>326</v>
-      </c>
-      <c r="L164" t="s">
-        <v>327</v>
       </c>
       <c r="M164" t="n">
         <v>17.73</v>
@@ -19184,13 +19181,13 @@
         <v>10</v>
       </c>
       <c r="D165" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E165" t="n">
         <v>350</v>
       </c>
       <c r="F165" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G165" t="s">
         <v>41</v>
@@ -19203,10 +19200,10 @@
         <v>8</v>
       </c>
       <c r="K165" t="s">
+        <v>327</v>
+      </c>
+      <c r="L165" t="s">
         <v>328</v>
-      </c>
-      <c r="L165" t="s">
-        <v>329</v>
       </c>
       <c r="M165" t="n">
         <v>24.86</v>
@@ -19293,13 +19290,13 @@
         <v>10</v>
       </c>
       <c r="D166" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E166" t="n">
         <v>350</v>
       </c>
       <c r="F166" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G166" t="s">
         <v>41</v>
@@ -19312,7 +19309,7 @@
         <v>6</v>
       </c>
       <c r="K166" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L166" t="s">
         <v>249</v>
@@ -19404,7 +19401,7 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E167" t="n">
         <v>350</v>
@@ -19423,10 +19420,10 @@
         <v>6</v>
       </c>
       <c r="K167" t="s">
+        <v>331</v>
+      </c>
+      <c r="L167" t="s">
         <v>332</v>
-      </c>
-      <c r="L167" t="s">
-        <v>333</v>
       </c>
       <c r="M167" t="n">
         <v>1.81</v>
@@ -19515,7 +19512,7 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E168" t="n">
         <v>350</v>
@@ -19534,7 +19531,7 @@
         <v>4</v>
       </c>
       <c r="K168" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L168" t="s">
         <v>243</v>
@@ -19626,7 +19623,7 @@
         <v>11</v>
       </c>
       <c r="D169" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E169" t="n">
         <v>350</v>
@@ -19645,7 +19642,7 @@
         <v>1</v>
       </c>
       <c r="K169" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L169" t="s">
         <v>221</v>
@@ -19737,7 +19734,7 @@
         <v>11</v>
       </c>
       <c r="D170" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E170" t="n">
         <v>350</v>
@@ -19756,7 +19753,7 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L170" t="s">
         <v>219</v>
@@ -19848,7 +19845,7 @@
         <v>11</v>
       </c>
       <c r="D171" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E171" t="n">
         <v>350</v>
@@ -19867,10 +19864,10 @@
         <v>8</v>
       </c>
       <c r="K171" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L171" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M171" t="n">
         <v>17.87</v>
@@ -19959,7 +19956,7 @@
         <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E172" t="n">
         <v>350</v>
@@ -19978,10 +19975,10 @@
         <v>2</v>
       </c>
       <c r="K172" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L172" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M172" t="n">
         <v>41.36</v>
@@ -20070,7 +20067,7 @@
         <v>11</v>
       </c>
       <c r="D173" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E173" t="n">
         <v>350</v>
@@ -20089,7 +20086,7 @@
         <v>7</v>
       </c>
       <c r="K173" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L173" t="s">
         <v>223</v>
@@ -20181,7 +20178,7 @@
         <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E174" t="n">
         <v>350</v>
@@ -20200,7 +20197,7 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L174" t="s">
         <v>219</v>
@@ -20292,7 +20289,7 @@
         <v>12</v>
       </c>
       <c r="D175" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E175" t="n">
         <v>350</v>
@@ -20311,10 +20308,10 @@
         <v>2</v>
       </c>
       <c r="K175" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L175" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M175" t="n">
         <v>6.59</v>
@@ -20385,7 +20382,7 @@
         <v>12</v>
       </c>
       <c r="D176" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E176" t="n">
         <v>350</v>
@@ -20404,10 +20401,10 @@
         <v>8</v>
       </c>
       <c r="K176" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L176" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M176" t="n">
         <v>8.02</v>
@@ -20496,7 +20493,7 @@
         <v>12</v>
       </c>
       <c r="D177" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E177" t="n">
         <v>350</v>
@@ -20515,7 +20512,7 @@
         <v>7</v>
       </c>
       <c r="K177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L177" t="s">
         <v>223</v>
@@ -20607,7 +20604,7 @@
         <v>12</v>
       </c>
       <c r="D178" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E178" t="n">
         <v>350</v>
@@ -20626,7 +20623,7 @@
         <v>4</v>
       </c>
       <c r="K178" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L178" t="s">
         <v>256</v>
@@ -20718,7 +20715,7 @@
         <v>12</v>
       </c>
       <c r="D179" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E179" t="n">
         <v>350</v>
@@ -20737,10 +20734,10 @@
         <v>6</v>
       </c>
       <c r="K179" t="s">
+        <v>345</v>
+      </c>
+      <c r="L179" t="s">
         <v>346</v>
-      </c>
-      <c r="L179" t="s">
-        <v>347</v>
       </c>
       <c r="M179" t="n">
         <v>34.27</v>
@@ -20829,7 +20826,7 @@
         <v>12</v>
       </c>
       <c r="D180" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E180" t="n">
         <v>350</v>
@@ -20848,10 +20845,10 @@
         <v>1</v>
       </c>
       <c r="K180" t="s">
+        <v>347</v>
+      </c>
+      <c r="L180" t="s">
         <v>348</v>
-      </c>
-      <c r="L180" t="s">
-        <v>349</v>
       </c>
       <c r="M180" t="n">
         <v>51.5</v>
